--- a/Team-Data/2008-09/2-17-2008-09.xlsx
+++ b/Team-Data/2008-09/2-17-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
         <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.585</v>
+        <v>0.596</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="O2" t="n">
         <v>19.1</v>
@@ -700,91 +767,91 @@
         <v>25.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R2" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S2" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T2" t="n">
         <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V2" t="n">
         <v>12.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -793,28 +860,28 @@
         <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB2" t="n">
         <v>15</v>
       </c>
-      <c r="BB2" t="n">
-        <v>18</v>
-      </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.796</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.387</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.776</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
@@ -903,34 +970,34 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM3" t="n">
         <v>19</v>
@@ -957,10 +1024,10 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -969,19 +1036,19 @@
         <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
         <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.396</v>
+        <v>0.404</v>
       </c>
       <c r="H4" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J4" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="K4" t="n">
         <v>0.451</v>
@@ -1058,22 +1125,22 @@
         <v>0.364</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.736</v>
+        <v>0.74</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T4" t="n">
-        <v>39.3</v>
+        <v>39</v>
       </c>
       <c r="U4" t="n">
         <v>21</v>
@@ -1085,34 +1152,34 @@
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1124,25 +1191,25 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN4" t="n">
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
@@ -1157,7 +1224,7 @@
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -1207,91 +1274,91 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.423</v>
+        <v>0.434</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
         <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1309,19 +1376,19 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM5" t="n">
         <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1330,7 +1397,7 @@
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1339,13 +1406,13 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,7 +1421,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -1389,103 +1456,103 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.784</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1497,46 +1564,46 @@
         <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
       </c>
       <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4</v>
       </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1676,13 +1743,13 @@
         <v>13</v>
       </c>
       <c r="AM7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="n">
         <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1691,10 +1758,10 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1858,10 +1925,10 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN8" t="n">
         <v>17</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>15</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
@@ -1882,10 +1949,10 @@
         <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.519</v>
+        <v>0.529</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1965,34 +2032,34 @@
         <v>13.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R9" t="n">
         <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T9" t="n">
         <v>40.6</v>
       </c>
       <c r="U9" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V9" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X9" t="n">
         <v>4.8</v>
@@ -2004,37 +2071,37 @@
         <v>21.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
         <v>27</v>
@@ -2046,22 +2113,22 @@
         <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
         <v>24</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
@@ -2070,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2268,7 @@
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
@@ -2213,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
         <v>15</v>
@@ -2222,10 +2289,10 @@
         <v>14</v>
       </c>
       <c r="AM10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2234,16 +2301,16 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
         <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.611</v>
+        <v>0.604</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J11" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.445</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M11" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="O11" t="n">
         <v>19.8</v>
       </c>
       <c r="P11" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T11" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V11" t="n">
         <v>14.1</v>
@@ -2362,22 +2429,22 @@
         <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2389,25 +2456,25 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
         <v>10</v>
@@ -2419,22 +2486,22 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2446,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB11" t="n">
         <v>18</v>
       </c>
-      <c r="BB11" t="n">
-        <v>17</v>
-      </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -2481,19 +2548,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="H12" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I12" t="n">
         <v>38.8</v>
@@ -2502,40 +2569,40 @@
         <v>85.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M12" t="n">
         <v>21.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="P12" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
@@ -2544,43 +2611,43 @@
         <v>5.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
         <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.7</v>
+        <v>104.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2601,7 +2668,7 @@
         <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>
@@ -2610,13 +2677,13 @@
         <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2625,16 +2692,16 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -2663,19 +2730,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>0.241</v>
+        <v>0.245</v>
       </c>
       <c r="H13" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I13" t="n">
         <v>35.7</v>
@@ -2687,37 +2754,37 @@
         <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M13" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
         <v>22.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R13" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S13" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="T13" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="U13" t="n">
         <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2726,7 +2793,7 @@
         <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z13" t="n">
         <v>21</v>
@@ -2735,13 +2802,13 @@
         <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2753,7 +2820,7 @@
         <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2768,19 +2835,19 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
         <v>25</v>
       </c>
       <c r="AO13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
@@ -2789,22 +2856,22 @@
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU13" t="n">
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2813,10 +2880,10 @@
         <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -2860,46 +2927,46 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J14" t="n">
-        <v>85</v>
+        <v>84.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L14" t="n">
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
         <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
         <v>8.300000000000001</v>
@@ -2911,7 +2978,7 @@
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA14" t="n">
         <v>22.9</v>
@@ -2920,10 +2987,10 @@
         <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,13 +3029,13 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,10 +3056,10 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.283</v>
+        <v>0.288</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
@@ -3051,61 +3118,61 @@
         <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M15" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P15" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S15" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T15" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U15" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3120,13 +3187,13 @@
         <v>10</v>
       </c>
       <c r="AI15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ15" t="n">
         <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3141,34 +3208,34 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT15" t="n">
         <v>26</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>27</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>23</v>
       </c>
       <c r="AY15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3323,13 +3390,13 @@
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ16" t="n">
         <v>27</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
         <v>23</v>
@@ -3347,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -3394,58 +3461,58 @@
         <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.491</v>
+        <v>0.473</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L17" t="n">
         <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
         <v>0.359</v>
       </c>
       <c r="O17" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,22 +3524,22 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="AA17" t="n">
         <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
@@ -3484,13 +3551,13 @@
         <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3505,16 +3572,16 @@
         <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
@@ -3523,10 +3590,10 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3535,13 +3602,13 @@
         <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>0.327</v>
+        <v>0.333</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,7 +3658,7 @@
         <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K18" t="n">
         <v>0.439</v>
@@ -3600,64 +3667,64 @@
         <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
         <v>42.2</v>
       </c>
       <c r="U18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
         <v>14.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>25</v>
@@ -3678,37 +3745,37 @@
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
         <v>28</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
       </c>
       <c r="AR18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
         <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>25</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -3755,91 +3822,91 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.444</v>
+        <v>0.453</v>
       </c>
       <c r="H19" t="n">
         <v>48.6</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
         <v>80.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L19" t="n">
         <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.383</v>
+        <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P19" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="S19" t="n">
         <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U19" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W19" t="n">
         <v>6.9</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
         <v>20.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3848,34 +3915,34 @@
         <v>7</v>
       </c>
       <c r="AI19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK19" t="n">
         <v>27</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>28</v>
-      </c>
       <c r="AL19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM19" t="n">
         <v>6</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AN19" t="n">
         <v>8</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>6</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
         <v>19</v>
@@ -3890,10 +3957,10 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
@@ -3902,13 +3969,13 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
         <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -3937,43 +4004,43 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.608</v>
+        <v>0.6</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J20" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q20" t="n">
         <v>0.8149999999999999</v>
@@ -3982,16 +4049,16 @@
         <v>9.5</v>
       </c>
       <c r="S20" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T20" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="U20" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
@@ -4000,7 +4067,7 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z20" t="n">
         <v>20.6</v>
@@ -4009,19 +4076,19 @@
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC20" t="n">
         <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>9</v>
@@ -4030,7 +4097,7 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
@@ -4042,13 +4109,13 @@
         <v>9</v>
       </c>
       <c r="AM20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4060,7 +4127,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
         <v>30</v>
@@ -4072,19 +4139,19 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -4119,52 +4186,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
         <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>0.415</v>
+        <v>0.404</v>
       </c>
       <c r="H21" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J21" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L21" t="n">
         <v>10.3</v>
       </c>
       <c r="M21" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
         <v>0.358</v>
       </c>
       <c r="O21" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P21" t="n">
         <v>22.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.796</v>
+        <v>0.799</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T21" t="n">
         <v>42.5</v>
@@ -4176,7 +4243,7 @@
         <v>14.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X21" t="n">
         <v>2.4</v>
@@ -4191,16 +4258,16 @@
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.2</v>
+        <v>105.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.5</v>
+        <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
@@ -4209,7 +4276,7 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4218,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>2</v>
@@ -4233,7 +4300,7 @@
         <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
@@ -4251,16 +4318,16 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
-        <v>0.241</v>
+        <v>0.245</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J22" t="n">
         <v>81.59999999999999</v>
@@ -4325,13 +4392,13 @@
         <v>0.449</v>
       </c>
       <c r="L22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O22" t="n">
         <v>20.1</v>
@@ -4340,7 +4407,7 @@
         <v>26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R22" t="n">
         <v>12.1</v>
@@ -4355,13 +4422,13 @@
         <v>20.3</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W22" t="n">
         <v>6.8</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" t="n">
         <v>5.2</v>
@@ -4379,7 +4446,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,13 +4461,13 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,13 +4476,13 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
@@ -4427,25 +4494,25 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
         <v>22</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4550,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" t="n">
         <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>0.75</v>
+        <v>0.745</v>
       </c>
       <c r="H23" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I23" t="n">
         <v>36.1</v>
@@ -4516,10 +4583,10 @@
         <v>0.396</v>
       </c>
       <c r="O23" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="P23" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.722</v>
@@ -4528,10 +4595,10 @@
         <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
         <v>19.3</v>
@@ -4543,7 +4610,7 @@
         <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
         <v>3.8</v>
@@ -4552,16 +4619,16 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC23" t="n">
         <v>8.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
         <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.519</v>
+        <v>0.529</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,10 +4750,10 @@
         <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
@@ -4695,73 +4762,73 @@
         <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.318</v>
+        <v>0.322</v>
       </c>
       <c r="O24" t="n">
         <v>18.8</v>
       </c>
       <c r="P24" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R24" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S24" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T24" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U24" t="n">
         <v>20.8</v>
       </c>
       <c r="V24" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X24" t="n">
         <v>5.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA24" t="n">
         <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
         <v>12</v>
@@ -4782,13 +4849,13 @@
         <v>13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
@@ -4797,28 +4864,28 @@
         <v>16</v>
       </c>
       <c r="AV24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
         <v>8</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -4847,67 +4914,67 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.497</v>
+        <v>0.494</v>
       </c>
       <c r="L25" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M25" t="n">
         <v>16.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O25" t="n">
         <v>20.9</v>
       </c>
       <c r="P25" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V25" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
@@ -4919,13 +4986,13 @@
         <v>22.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.1</v>
+        <v>104.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,13 +5004,13 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4955,7 +5022,7 @@
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4970,22 +5037,22 @@
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -4997,10 +5064,10 @@
         <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E26" t="n">
         <v>32</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.627</v>
+        <v>0.615</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P26" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5092,25 +5159,25 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>21.2</v>
       </c>
-      <c r="AA26" t="n">
-        <v>21.3</v>
-      </c>
       <c r="AB26" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>7</v>
@@ -5119,16 +5186,16 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,40 +5204,40 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>17</v>
@@ -5179,10 +5246,10 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5359,7 @@
         <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF27" t="n">
         <v>30</v>
@@ -5301,10 +5368,10 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5316,7 +5383,7 @@
         <v>16</v>
       </c>
       <c r="AM27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN27" t="n">
         <v>21</v>
@@ -5346,22 +5413,22 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" t="n">
         <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.673</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
-        <v>79.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
         <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O28" t="n">
         <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T28" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U28" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V28" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W28" t="n">
         <v>5.9</v>
@@ -5456,22 +5523,22 @@
         <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA28" t="n">
         <v>18.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5480,7 +5547,7 @@
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5492,13 +5559,13 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>4</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
@@ -5516,13 +5583,13 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5534,7 +5601,7 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
@@ -5665,10 +5732,10 @@
         <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
         <v>23</v>
@@ -5683,7 +5750,7 @@
         <v>21</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
@@ -5775,7 +5842,7 @@
         <v>38.1</v>
       </c>
       <c r="J30" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.478</v>
@@ -5790,28 +5857,28 @@
         <v>0.34</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.77</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
         <v>11.8</v>
       </c>
       <c r="S30" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U30" t="n">
         <v>24.6</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
         <v>8.6</v>
@@ -5829,16 +5896,16 @@
         <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF30" t="n">
         <v>12</v>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
@@ -5898,7 +5965,7 @@
         <v>18</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.222</v>
+        <v>0.208</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5960,40 +6027,40 @@
         <v>81.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L31" t="n">
         <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N31" t="n">
         <v>0.328</v>
       </c>
       <c r="O31" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P31" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="T31" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U31" t="n">
         <v>20.5</v>
       </c>
       <c r="V31" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W31" t="n">
         <v>7.4</v>
@@ -6008,16 +6075,16 @@
         <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.7</v>
+        <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6038,13 +6105,13 @@
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
@@ -6053,16 +6120,16 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT31" t="n">
         <v>24</v>
@@ -6077,10 +6144,10 @@
         <v>12</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ31" t="n">
         <v>13</v>
@@ -6092,7 +6159,7 @@
         <v>26</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-17-2008-09</t>
+          <t>2009-02-17</t>
         </is>
       </c>
     </row>
